--- a/testcases/locations/location-account-address.xlsx
+++ b/testcases/locations/location-account-address.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M132"/>
+  <dimension ref="A1:M123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2965,12 +2965,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>TC-LOC-ACC-021</t>
+          <t xml:space="preserve">TC-LOC-ACC-021</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Verify Phone 1 reverts to the account phone after save and reload</t>
+          <t>Cancel Save dialog discards save without persisting</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2988,7 +2988,7 @@
           <t>User: automation user (location-edit permission)
 Location: test office 1604
 Application: Navigator
-Sample input 1: "Phone 1"
+Sample input 1: "Phone 2"
 Sample input 2: "Save Changes"</t>
         </is>
       </c>
@@ -3004,10 +3004,14 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Pending Automation</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="J67" t="inlineStr">
         <is>
           <t>Office 1604 is open in Navigator. Account and Address tab is active</t>
@@ -3015,19 +3019,15 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>1. Edit "Phone 1" with a test value and click outside the field to move focus away.</t>
+          <t>1. Edit "Phone 2" with a test value. Confirm "Save" becomes enabled.</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>Phone 1 updates to show the entered test value.</t>
-        </is>
-      </c>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>Not automated — the Phone 1 field is account-linked; the server restores the account's phone number on reload, so a saved change to this field cannot persist</t>
-        </is>
-      </c>
+          <t>The Save button becomes enabled.</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr"/>
@@ -3042,12 +3042,12 @@
       <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr">
         <is>
-          <t>2. Confirm "Save" becomes enabled, click "Save", and confirm the "Save Changes" dialog with "Save".</t>
+          <t>2. Click "Save". Confirm the "Save Changes" dialog appears.</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>The change is saved and the Save button becomes disabled.</t>
+          <t>The Save Changes dialog appears.</t>
         </is>
       </c>
       <c r="M68" t="inlineStr"/>
@@ -3065,12 +3065,12 @@
       <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr">
         <is>
-          <t>3. Reload the page and reopen the Account and Address tab.</t>
+          <t>3. Click "Cancel" in the dialog. Confirm the dialog closes.</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>The Account and Address tab opens and its content is displayed.</t>
+          <t>The Save Changes dialog closes.</t>
         </is>
       </c>
       <c r="M69" t="inlineStr"/>
@@ -3088,102 +3088,101 @@
       <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr">
         <is>
-          <t>4. Read the "Phone 1" value</t>
+          <t>4. Verify "Save" is still enabled and "Phone 2" still shows the typed value (changes not committed).</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>Phone 1 does not keep a manually entered value. After save and reload it shows the account's phone number, because Phone 1 is linked to the account</t>
+          <t>The Save button remains enabled and Phone 2 still shows the typed value.</t>
         </is>
       </c>
       <c r="M70" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>TC-LOC-ACC-022</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>Cancel Save dialog discards save without persisting</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
+      <c r="A71" t="inlineStr"/>
+      <c r="B71" t="inlineStr"/>
+      <c r="C71" t="inlineStr"/>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>5. Reload the page to discard changes</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>The page reloads with the original field values; the unsaved change is not present.</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-LOC-ACC-022</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Phone 1 cleared shows invalid state and error icon</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
         <is>
           <t>locations</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr">
+      <c r="D72" t="inlineStr">
         <is>
           <t>account_address</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
+      <c r="E72" t="inlineStr">
         <is>
           <t>User: automation user (location-edit permission)
 Location: test office 1604
 Application: Navigator
-Sample input 1: "Phone 2"
-Sample input 2: "Save Changes"</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
+Sample input 1: "Phone 1"</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr">
+      <c r="G72" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
+      <c r="H72" t="inlineStr">
         <is>
           <t>Automated</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr">
+      <c r="I72" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="J71" t="inlineStr">
+      <c r="J72" t="inlineStr">
         <is>
           <t>Office 1604 is open in Navigator. Account and Address tab is active</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>1. Edit "Phone 2" with a test value. Confirm "Save" becomes enabled.</t>
-        </is>
-      </c>
-      <c r="L71" t="inlineStr">
-        <is>
-          <t>The Save button becomes enabled.</t>
-        </is>
-      </c>
-      <c r="M71" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr"/>
-      <c r="B72" t="inlineStr"/>
-      <c r="C72" t="inlineStr"/>
-      <c r="D72" t="inlineStr"/>
-      <c r="E72" t="inlineStr"/>
-      <c r="F72" t="inlineStr"/>
-      <c r="G72" t="inlineStr"/>
-      <c r="H72" t="inlineStr"/>
-      <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr">
         <is>
-          <t>2. Click "Save". Confirm the "Save Changes" dialog appears.</t>
+          <t>1. Clear "Phone 1" and click outside the field to move focus away.</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>The Save Changes dialog appears.</t>
+          <t>The Phone 1 field becomes empty and loses focus.</t>
         </is>
       </c>
       <c r="M72" t="inlineStr"/>
@@ -3201,12 +3200,12 @@
       <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr">
         <is>
-          <t>3. Click "Cancel" in the dialog. Confirm the dialog closes.</t>
+          <t>2. Verify the field is marked invalid and the error icon is visible.</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>The Save Changes dialog closes.</t>
+          <t>The field is marked invalid and an error icon is displayed.</t>
         </is>
       </c>
       <c r="M73" t="inlineStr"/>
@@ -3224,12 +3223,12 @@
       <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr">
         <is>
-          <t>4. Verify "Save" is still enabled and "Phone 2" still shows the typed value (changes not committed).</t>
+          <t>3. Verify "Save" remains enabled (the application does not block save on an invalid Phone 1).</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>The Save button remains enabled and Phone 2 still shows the typed value.</t>
+          <t>The Save button remains enabled.</t>
         </is>
       </c>
       <c r="M74" t="inlineStr"/>
@@ -3247,12 +3246,12 @@
       <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr">
         <is>
-          <t>5. Reload the page to discard changes</t>
+          <t>4. Reload the page to restore the baseline</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>The page reloads with the original field values; the unsaved change is not present.</t>
+          <t>The page reloads and Phone 1 is restored to its original value.</t>
         </is>
       </c>
       <c r="M75" t="inlineStr"/>
@@ -3260,12 +3259,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>TC-LOC-ACC-023</t>
+          <t xml:space="preserve">TC-LOC-ACC-023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Phone 1 cleared shows invalid state and error icon</t>
+          <t>Account List Address filter returns matching results</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3283,7 +3282,9 @@
           <t>User: automation user (location-edit permission)
 Location: test office 1604
 Application: Navigator
-Sample input 1: "Phone 1"</t>
+Sample input 1: "Address"
+Sample input 2: "Beverly"
+Sample input 3: "Search"</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3303,7 +3304,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -3313,15 +3314,19 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>1. Clear "Phone 1" and click outside the field to move focus away.</t>
+          <t>1. Open the Account List dialog.</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>The Phone 1 field becomes empty and loses focus.</t>
-        </is>
-      </c>
-      <c r="M76" t="inlineStr"/>
+          <t>The Account List dialog opens.</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>Blocked — the Account List search returns no results for any search term, including the office's own existing account; the search comes back empty every time. Pending an application fix</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr"/>
@@ -3336,12 +3341,12 @@
       <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr">
         <is>
-          <t>2. Verify the field is marked invalid and the error icon is visible.</t>
+          <t>2. Fill the "Address" filter with "Beverly".</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>The field is marked invalid and an error icon is displayed.</t>
+          <t>"Beverly" is entered in the Address filter.</t>
         </is>
       </c>
       <c r="M77" t="inlineStr"/>
@@ -3359,12 +3364,12 @@
       <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr">
         <is>
-          <t>3. Verify "Save" remains enabled (the application does not block save on an invalid Phone 1).</t>
+          <t>3. Click "Search". Confirm the results are filtered.</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>The Save button remains enabled.</t>
+          <t>The results table updates with filtered matches.</t>
         </is>
       </c>
       <c r="M78" t="inlineStr"/>
@@ -3382,107 +3387,110 @@
       <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr">
         <is>
-          <t>4. Reload the page to restore the baseline</t>
+          <t>4. Verify the results contain "Beverly".</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>The page reloads and Phone 1 is restored to its original value.</t>
+          <t>The results table shows entries containing "Beverly".</t>
         </is>
       </c>
       <c r="M79" t="inlineStr"/>
     </row>
     <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>TC-LOC-ACC-024</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Unsaved-changes warning fires only when leaving the basic-info group, not between its sub-tabs</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
+      <c r="A80" t="inlineStr"/>
+      <c r="B80" t="inlineStr"/>
+      <c r="C80" t="inlineStr"/>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>5. Cancel the dialog</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>The Account List dialog closes.</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-LOC-ACC-024</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Account List City filter returns matching results</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
         <is>
           <t>locations</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr">
+      <c r="D81" t="inlineStr">
         <is>
           <t>account_address</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr">
+      <c r="E81" t="inlineStr">
         <is>
           <t>User: automation user (location-edit permission)
 Location: test office 1604
 Application: Navigator
-Sample input 1: "Phone 2"
-Sample input 2: "Unsaved changes"
-Sample input 3: "Stay"
-Sample input 4: "Discard"</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
+Sample input 1: "City"
+Sample input 2: "LOS ANGELES"
+Sample input 3: "Search"</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr">
+      <c r="G81" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>Pending Automation</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr">
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
         <is>
           <t>Office 1604 is open in Navigator. Account and Address tab is active</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>1. On the Account and Address sub-tab, edit "Phone 2" with a test value so "Save" becomes enabled (the left-panel form now has unsaved changes).</t>
-        </is>
-      </c>
-      <c r="L80" t="inlineStr">
-        <is>
-          <t>The Save button becomes enabled, indicating unsaved changes.</t>
-        </is>
-      </c>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>Not automated — switching tabs while there are unsaved changes does not trigger an Unsaved Changes prompt on this page, so there is no dialog behavior to verify</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr"/>
-      <c r="B81" t="inlineStr"/>
-      <c r="C81" t="inlineStr"/>
-      <c r="D81" t="inlineStr"/>
-      <c r="E81" t="inlineStr"/>
-      <c r="F81" t="inlineStr"/>
-      <c r="G81" t="inlineStr"/>
-      <c r="H81" t="inlineStr"/>
-      <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr">
         <is>
-          <t>2. Without saving, switch to another basic-info sub-tab (for example Local Information, Currency, Legal, or Notes). Confirm no warning appears and the edit is retained.</t>
+          <t>1. Open the Account List dialog.</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>No warning appears and the edited value is retained.</t>
-        </is>
-      </c>
-      <c r="M81" t="inlineStr"/>
+          <t>The Account List dialog opens.</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>Blocked — the Account List search returns no results for any search term, including the office's own existing account; the search comes back empty every time. Pending an application fix</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr"/>
@@ -3497,12 +3505,12 @@
       <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr">
         <is>
-          <t>3. Still without saving, switch away from the basic-info group - to another setup module such as Corporate Pricing, or to the Management History tab.</t>
+          <t>2. Fill the "City" filter with "LOS ANGELES".</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>Navigation away from the group is blocked and the Unsaved changes dialog begins to appear.</t>
+          <t>"LOS ANGELES" is entered in the City filter.</t>
         </is>
       </c>
       <c r="M82" t="inlineStr"/>
@@ -3520,12 +3528,12 @@
       <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr">
         <is>
-          <t>4. Observe the "Unsaved changes" dialog with "Stay" and "Discard" buttons.</t>
+          <t>3. Click "Search". Confirm the results are filtered.</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>The Unsaved changes dialog is displayed with Stay and Discard buttons.</t>
+          <t>The results table updates with filtered matches.</t>
         </is>
       </c>
       <c r="M83" t="inlineStr"/>
@@ -3543,107 +3551,102 @@
       <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr">
         <is>
-          <t>5. Reload the page to discard any remaining changes</t>
+          <t>4. Verify the results contain "LOS ANGELES".</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>The eight left-panel basic-info sub-tabs (Local Information, Currency, Pricing, Account and Address, Legal, Notes, Shared Setup Locations, Auto Add-On) share one global Save, so switching among them with unsaved changes shows no warning and the edits carry across sub-tabs - a single Save commits them all. Leaving that group - to another setup module such as Corporate Pricing, or to the Management History tab - shows an "Unsaved changes" dialog with "Stay" and "Discard" buttons</t>
+          <t>The results table shows entries containing "LOS ANGELES".</t>
         </is>
       </c>
       <c r="M84" t="inlineStr"/>
     </row>
     <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>TC-LOC-ACC-025</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>Account List Address filter returns matching results</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
+      <c r="A85" t="inlineStr"/>
+      <c r="B85" t="inlineStr"/>
+      <c r="C85" t="inlineStr"/>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr"/>
+      <c r="F85" t="inlineStr"/>
+      <c r="G85" t="inlineStr"/>
+      <c r="H85" t="inlineStr"/>
+      <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>5. Cancel the dialog</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>The Account List dialog closes.</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-LOC-ACC-025</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Address selection changes venue display fields</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
         <is>
           <t>locations</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr">
+      <c r="D86" t="inlineStr">
         <is>
           <t>account_address</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr">
+      <c r="E86" t="inlineStr">
         <is>
           <t>User: automation user (location-edit permission)
 Location: test office 1604
 Application: Navigator
-Sample input 1: "Address"
-Sample input 2: "Beverly"
-Sample input 3: "Search"</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
+Sample input 1: "WEST HOLLYWOOD"
+Sample input 2: "PALM SPRINGS"</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr">
+      <c r="G86" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
+      <c r="H86" t="inlineStr">
         <is>
           <t>Automated</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>Blocked</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr">
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
         <is>
           <t>Office 1604 is open in Navigator. Account and Address tab is active</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>1. Open the Account List dialog.</t>
-        </is>
-      </c>
-      <c r="L85" t="inlineStr">
-        <is>
-          <t>The Account List dialog opens.</t>
-        </is>
-      </c>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>Blocked — the Account List search returns no results for any search term, including the office's own existing account; the search comes back empty every time. Pending an application fix</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr"/>
-      <c r="B86" t="inlineStr"/>
-      <c r="C86" t="inlineStr"/>
-      <c r="D86" t="inlineStr"/>
-      <c r="E86" t="inlineStr"/>
-      <c r="F86" t="inlineStr"/>
-      <c r="G86" t="inlineStr"/>
-      <c r="H86" t="inlineStr"/>
-      <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr">
         <is>
-          <t>2. Fill the "Address" filter with "Beverly".</t>
+          <t>1. Verify starting city is "WEST HOLLYWOOD"</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>"Beverly" is entered in the Address filter.</t>
+          <t>The city field displays "WEST HOLLYWOOD".</t>
         </is>
       </c>
       <c r="M86" t="inlineStr"/>
@@ -3661,12 +3664,12 @@
       <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr">
         <is>
-          <t>3. Click "Search". Confirm the results are filtered.</t>
+          <t>2. Open Venue Address dialog</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>The results table updates with filtered matches.</t>
+          <t>The Select Customer Address dialog opens.</t>
         </is>
       </c>
       <c r="M87" t="inlineStr"/>
@@ -3684,12 +3687,12 @@
       <c r="J88" t="inlineStr"/>
       <c r="K88" t="inlineStr">
         <is>
-          <t>4. Verify the results contain "Beverly".</t>
+          <t>3. Select alternate address row (4200 E Palm Canyon Dr)</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>The results table shows entries containing "Beverly".</t>
+          <t>The row for "4200 E Palm Canyon Dr" becomes selected.</t>
         </is>
       </c>
       <c r="M88" t="inlineStr"/>
@@ -3707,87 +3710,38 @@
       <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr">
         <is>
-          <t>5. Cancel the dialog</t>
+          <t>4. Verify city changed to "PALM SPRINGS"</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>The Account List dialog closes.</t>
+          <t>The city field updates to display "PALM SPRINGS".</t>
         </is>
       </c>
       <c r="M89" t="inlineStr"/>
     </row>
     <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>TC-LOC-ACC-026</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>Account List City filter returns matching results</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>locations</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>account_address</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>User: automation user (location-edit permission)
-Location: test office 1604
-Application: Navigator
-Sample input 1: "City"
-Sample input 2: "LOS ANGELES"
-Sample input 3: "Search"</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>Automated</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>Blocked</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>Office 1604 is open in Navigator. Account and Address tab is active</t>
-        </is>
-      </c>
+      <c r="A90" t="inlineStr"/>
+      <c r="B90" t="inlineStr"/>
+      <c r="C90" t="inlineStr"/>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="inlineStr"/>
+      <c r="F90" t="inlineStr"/>
+      <c r="G90" t="inlineStr"/>
+      <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr">
         <is>
-          <t>1. Open the Account List dialog.</t>
+          <t>5. Verify Save becomes enabled</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>The Account List dialog opens.</t>
-        </is>
-      </c>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>Blocked — the Account List search returns no results for any search term, including the office's own existing account; the search comes back empty every time. Pending an application fix</t>
-        </is>
-      </c>
+          <t>The Save button becomes enabled.</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr"/>
@@ -3802,38 +3756,84 @@
       <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr">
         <is>
-          <t>2. Fill the "City" filter with "LOS ANGELES".</t>
+          <t>6. Reload to discard - verify city restored to "WEST HOLLYWOOD"</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>"LOS ANGELES" is entered in the City filter.</t>
+          <t>Address selection updates display fields but changes are discarded on reload (the address change is not actually saved, so it is lost on reload)</t>
         </is>
       </c>
       <c r="M91" t="inlineStr"/>
     </row>
     <row r="92">
-      <c r="A92" t="inlineStr"/>
-      <c r="B92" t="inlineStr"/>
-      <c r="C92" t="inlineStr"/>
-      <c r="D92" t="inlineStr"/>
-      <c r="E92" t="inlineStr"/>
-      <c r="F92" t="inlineStr"/>
-      <c r="G92" t="inlineStr"/>
-      <c r="H92" t="inlineStr"/>
-      <c r="I92" t="inlineStr"/>
-      <c r="J92" t="inlineStr"/>
+      <c r="A92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-LOC-ACC-026</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Account selection changes venue name and persists</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>locations</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>account_address</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>User: automation user (location-edit permission)
+Location: test office 1604
+Application: Navigator</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>Office 1604 is open in Navigator. Account and Address tab is active</t>
+        </is>
+      </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>3. Click "Search". Confirm the results are filtered.</t>
+          <t>1. Open the Account List, search for the current account, and select it (re-selecting triggers unsaved changes).</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>The results table updates with filtered matches.</t>
-        </is>
-      </c>
-      <c r="M92" t="inlineStr"/>
+          <t>The current venue name is read from the Name field and stored for restoration.</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>Blocked — the Account List search returns no results for any search term, including the office's own existing account; the search comes back empty every time. Pending an application fix</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr"/>
@@ -3848,12 +3848,12 @@
       <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr">
         <is>
-          <t>4. Verify the results contain "LOS ANGELES".</t>
+          <t>2. Verify "Save" becomes enabled.</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>The results table shows entries containing "LOS ANGELES".</t>
+          <t>The Account List opens, the current account is located and selected, and the dialog closes.</t>
         </is>
       </c>
       <c r="M93" t="inlineStr"/>
@@ -3871,105 +3871,110 @@
       <c r="J94" t="inlineStr"/>
       <c r="K94" t="inlineStr">
         <is>
-          <t>5. Cancel the dialog</t>
+          <t>3. Click "Save" and confirm.</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>The Account List dialog closes.</t>
+          <t>The Save button becomes enabled.</t>
         </is>
       </c>
       <c r="M94" t="inlineStr"/>
     </row>
     <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>TC-LOC-ACC-027</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>Address selection changes venue display fields</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
+      <c r="A95" t="inlineStr"/>
+      <c r="B95" t="inlineStr"/>
+      <c r="C95" t="inlineStr"/>
+      <c r="D95" t="inlineStr"/>
+      <c r="E95" t="inlineStr"/>
+      <c r="F95" t="inlineStr"/>
+      <c r="G95" t="inlineStr"/>
+      <c r="H95" t="inlineStr"/>
+      <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>4. Reload the page and verify the venue name persisted</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>The Save Changes dialog is confirmed and the change is committed.</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-LOC-ACC-027</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Phone 2 cleared value persists empty after reload</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
         <is>
           <t>locations</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr">
+      <c r="D96" t="inlineStr">
         <is>
           <t>account_address</t>
         </is>
       </c>
-      <c r="E95" t="inlineStr">
+      <c r="E96" t="inlineStr">
         <is>
           <t>User: automation user (location-edit permission)
 Location: test office 1604
 Application: Navigator
-Sample input 1: "WEST HOLLYWOOD"
-Sample input 2: "PALM SPRINGS"</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
+Sample input 1: "Phone 2"
+Sample input 2: "Save Changes"
+Sample input 3: "Account and Address"</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr">
+      <c r="G96" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
+      <c r="H96" t="inlineStr">
         <is>
           <t>Automated</t>
         </is>
       </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
         <is>
           <t>Office 1604 is open in Navigator. Account and Address tab is active</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t>1. Verify starting city is "WEST HOLLYWOOD"</t>
-        </is>
-      </c>
-      <c r="L95" t="inlineStr">
-        <is>
-          <t>The city field displays "WEST HOLLYWOOD".</t>
-        </is>
-      </c>
-      <c r="M95" t="inlineStr"/>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr"/>
-      <c r="B96" t="inlineStr"/>
-      <c r="C96" t="inlineStr"/>
-      <c r="D96" t="inlineStr"/>
-      <c r="E96" t="inlineStr"/>
-      <c r="F96" t="inlineStr"/>
-      <c r="G96" t="inlineStr"/>
-      <c r="H96" t="inlineStr"/>
-      <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr">
         <is>
-          <t>2. Open Venue Address dialog</t>
+          <t>1. Baseline: seed "Phone 2" with a value and save (so that clearing it is a real change).</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>The Select Customer Address dialog opens.</t>
-        </is>
-      </c>
-      <c r="M96" t="inlineStr"/>
+          <t>Phone 2 is saved with the seeded value.</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>Blocked — clearing the Phone 2 field and saving does not persist the empty value; the previous value reappears after reload. Pending an application fix</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr"/>
@@ -3984,12 +3989,12 @@
       <c r="J97" t="inlineStr"/>
       <c r="K97" t="inlineStr">
         <is>
-          <t>3. Select alternate address row (4200 E Palm Canyon Dr)</t>
+          <t>2. Clear "Phone 2" and click outside the field to move focus away. Confirm "Save" becomes enabled.</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>The row for "4200 E Palm Canyon Dr" becomes selected.</t>
+          <t>The Save button becomes enabled.</t>
         </is>
       </c>
       <c r="M97" t="inlineStr"/>
@@ -4007,12 +4012,12 @@
       <c r="J98" t="inlineStr"/>
       <c r="K98" t="inlineStr">
         <is>
-          <t>4. Verify city changed to "PALM SPRINGS"</t>
+          <t>3. Click "Save" and confirm the "Save Changes" dialog. Confirm "Save" becomes disabled.</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>The city field updates to display "PALM SPRINGS".</t>
+          <t>The Save button becomes disabled after the changes are saved.</t>
         </is>
       </c>
       <c r="M98" t="inlineStr"/>
@@ -4030,12 +4035,12 @@
       <c r="J99" t="inlineStr"/>
       <c r="K99" t="inlineStr">
         <is>
-          <t>5. Verify Save becomes enabled</t>
+          <t>4. Reload the page and navigate back to the "Account and Address" tab.</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>The Save button becomes enabled.</t>
+          <t>The Account and Address tab opens and its content is displayed.</t>
         </is>
       </c>
       <c r="M99" t="inlineStr"/>
@@ -4053,12 +4058,12 @@
       <c r="J100" t="inlineStr"/>
       <c r="K100" t="inlineStr">
         <is>
-          <t>6. Reload to discard - verify city restored to "WEST HOLLYWOOD"</t>
+          <t>5. Verify "Phone 2" is empty (the cleared value persisted)</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>Address selection updates display fields but changes are discarded on reload (the address change is not actually saved, so it is lost on reload)</t>
+          <t>Phone 2 is empty; the cleared value persisted through save and reload.</t>
         </is>
       </c>
       <c r="M100" t="inlineStr"/>
@@ -4066,12 +4071,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>TC-LOC-ACC-028</t>
+          <t xml:space="preserve">TC-LOC-ACC-028</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Account selection changes venue name and persists</t>
+          <t>Account List Account Number filter returns matching account</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -4088,7 +4093,12 @@
         <is>
           <t>User: automation user (location-edit permission)
 Location: test office 1604
-Application: Navigator</t>
+Application: Navigator
+Sample input 1: "Name"
+Sample input 2: "Account Number"
+Sample input 3: "AC000107"
+Sample input 4: "Search"
+Sample input 5: "Parker Palm Springs"</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -4118,12 +4128,12 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>1. Open the Account List, search for the current account, and select it (re-selecting triggers unsaved changes).</t>
+          <t>1. Open the Account List dialog via the "Name" button.</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>The current venue name is read from the Name field and stored for restoration.</t>
+          <t>The Account List dialog opens.</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
@@ -4145,12 +4155,12 @@
       <c r="J102" t="inlineStr"/>
       <c r="K102" t="inlineStr">
         <is>
-          <t>2. Verify "Save" becomes enabled.</t>
+          <t>2. Fill the "Account Number" filter with "AC000107".</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>The Account List opens, the current account is located and selected, and the dialog closes.</t>
+          <t>"AC000107" is entered in the Account Number filter.</t>
         </is>
       </c>
       <c r="M102" t="inlineStr"/>
@@ -4168,12 +4178,12 @@
       <c r="J103" t="inlineStr"/>
       <c r="K103" t="inlineStr">
         <is>
-          <t>3. Click "Save" and confirm.</t>
+          <t>3. Click "Search". Confirm the results are filtered (allow up to 20 seconds for the server search).</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>The Save button becomes enabled.</t>
+          <t>The results table updates with the filtered match.</t>
         </is>
       </c>
       <c r="M103" t="inlineStr"/>
@@ -4191,107 +4201,103 @@
       <c r="J104" t="inlineStr"/>
       <c r="K104" t="inlineStr">
         <is>
-          <t>4. Reload the page and verify the venue name persisted</t>
+          <t>4. Verify the results contain "Parker Palm Springs".</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>The Save Changes dialog is confirmed and the change is committed.</t>
+          <t>The results table shows the entry "Parker Palm Springs".</t>
         </is>
       </c>
       <c r="M104" t="inlineStr"/>
     </row>
     <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>TC-LOC-ACC-029</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>Phone 2 cleared value persists empty after reload</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
+      <c r="A105" t="inlineStr"/>
+      <c r="B105" t="inlineStr"/>
+      <c r="C105" t="inlineStr"/>
+      <c r="D105" t="inlineStr"/>
+      <c r="E105" t="inlineStr"/>
+      <c r="F105" t="inlineStr"/>
+      <c r="G105" t="inlineStr"/>
+      <c r="H105" t="inlineStr"/>
+      <c r="I105" t="inlineStr"/>
+      <c r="J105" t="inlineStr"/>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>5. Cancel the dialog</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>The Account List dialog closes.</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-LOC-ACC-029</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Address dialog search filter then clear restores full set</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
         <is>
           <t>locations</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr">
+      <c r="D106" t="inlineStr">
         <is>
           <t>account_address</t>
         </is>
       </c>
-      <c r="E105" t="inlineStr">
+      <c r="E106" t="inlineStr">
         <is>
           <t>User: automation user (location-edit permission)
 Location: test office 1604
 Application: Navigator
-Sample input 1: "Phone 2"
-Sample input 2: "Save Changes"
-Sample input 3: "Account and Address"</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
+Sample input 1: "Select Customer Address"
+Sample input 2: "Address"
+Sample input 3: "Beverly"</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="G105" t="inlineStr">
+      <c r="G106" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr">
+      <c r="H106" t="inlineStr">
         <is>
           <t>Automated</t>
         </is>
       </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>Blocked</t>
-        </is>
-      </c>
-      <c r="J105" t="inlineStr">
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
         <is>
           <t>Office 1604 is open in Navigator. Account and Address tab is active</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr">
-        <is>
-          <t>1. Baseline: seed "Phone 2" with a value and save (so that clearing it is a real change).</t>
-        </is>
-      </c>
-      <c r="L105" t="inlineStr">
-        <is>
-          <t>Phone 2 is saved with the seeded value.</t>
-        </is>
-      </c>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>Blocked — clearing the Phone 2 field and saving does not persist the empty value; the previous value reappears after reload. Pending an application fix</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr"/>
-      <c r="B106" t="inlineStr"/>
-      <c r="C106" t="inlineStr"/>
-      <c r="D106" t="inlineStr"/>
-      <c r="E106" t="inlineStr"/>
-      <c r="F106" t="inlineStr"/>
-      <c r="G106" t="inlineStr"/>
-      <c r="H106" t="inlineStr"/>
-      <c r="I106" t="inlineStr"/>
-      <c r="J106" t="inlineStr"/>
       <c r="K106" t="inlineStr">
         <is>
-          <t>2. Clear "Phone 2" and click outside the field to move focus away. Confirm "Save" becomes enabled.</t>
+          <t>1. Open the "Select Customer Address" dialog from the Venue "Address" button. Confirm 7 rows are visible (Total Addresses: 7).</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>The Save button becomes enabled.</t>
+          <t>Seven address rows are displayed with "Total Addresses: 7" shown in the footer.</t>
         </is>
       </c>
       <c r="M106" t="inlineStr"/>
@@ -4309,12 +4315,12 @@
       <c r="J107" t="inlineStr"/>
       <c r="K107" t="inlineStr">
         <is>
-          <t>3. Click "Save" and confirm the "Save Changes" dialog. Confirm "Save" becomes disabled.</t>
+          <t>2. Type "Beverly" in the search bar. Confirm the rows are reduced by the filter.</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>The Save button becomes disabled after the changes are saved.</t>
+          <t>The row count reduces to matches containing "Beverly".</t>
         </is>
       </c>
       <c r="M107" t="inlineStr"/>
@@ -4332,12 +4338,12 @@
       <c r="J108" t="inlineStr"/>
       <c r="K108" t="inlineStr">
         <is>
-          <t>4. Reload the page and navigate back to the "Account and Address" tab.</t>
+          <t>3. Clear the search bar.</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>The Account and Address tab opens and its content is displayed.</t>
+          <t>The search bar becomes empty.</t>
         </is>
       </c>
       <c r="M108" t="inlineStr"/>
@@ -4355,109 +4361,106 @@
       <c r="J109" t="inlineStr"/>
       <c r="K109" t="inlineStr">
         <is>
-          <t>5. Verify "Phone 2" is empty (the cleared value persisted)</t>
+          <t>4. Verify the rows restore to the full 7-row set.</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>Phone 2 is empty; the cleared value persisted through save and reload.</t>
+          <t>The full set of 7 address rows is restored.</t>
         </is>
       </c>
       <c r="M109" t="inlineStr"/>
     </row>
     <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>TC-LOC-ACC-030</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>Account List Account Number filter returns matching account</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
+      <c r="A110" t="inlineStr"/>
+      <c r="B110" t="inlineStr"/>
+      <c r="C110" t="inlineStr"/>
+      <c r="D110" t="inlineStr"/>
+      <c r="E110" t="inlineStr"/>
+      <c r="F110" t="inlineStr"/>
+      <c r="G110" t="inlineStr"/>
+      <c r="H110" t="inlineStr"/>
+      <c r="I110" t="inlineStr"/>
+      <c r="J110" t="inlineStr"/>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>5. Cancel the dialog</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>The Account List dialog closes.</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-LOC-ACC-030</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Master Bill To selection updates Master display + leaves Venue unchanged + enables Save</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
         <is>
           <t>locations</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr">
+      <c r="D111" t="inlineStr">
         <is>
           <t>account_address</t>
         </is>
       </c>
-      <c r="E110" t="inlineStr">
+      <c r="E111" t="inlineStr">
         <is>
           <t>User: automation user (location-edit permission)
 Location: test office 1604
 Application: Navigator
-Sample input 1: "Name"
-Sample input 2: "Account Number"
-Sample input 3: "AC000107"
-Sample input 4: "Search"
-Sample input 5: "Parker Palm Springs"</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
+Sample input 1: "WEST HOLLYWOOD"
+Sample input 2: "Master"
+Sample input 3: "4200 E Palm Canyon Dr"
+Sample input 4: "Select"
+Sample input 5: "PALM SPRINGS"
+Sample input 6: "Venue/Branch"</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="G110" t="inlineStr">
+      <c r="G111" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H110" t="inlineStr">
+      <c r="H111" t="inlineStr">
         <is>
           <t>Automated</t>
         </is>
       </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>Blocked</t>
-        </is>
-      </c>
-      <c r="J110" t="inlineStr">
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
         <is>
           <t>Office 1604 is open in Navigator. Account and Address tab is active</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr">
-        <is>
-          <t>1. Open the Account List dialog via the "Name" button.</t>
-        </is>
-      </c>
-      <c r="L110" t="inlineStr">
-        <is>
-          <t>The Account List dialog opens.</t>
-        </is>
-      </c>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>Blocked — the Account List search returns no results for any search term, including the office's own existing account; the search comes back empty every time. Pending an application fix</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr"/>
-      <c r="B111" t="inlineStr"/>
-      <c r="C111" t="inlineStr"/>
-      <c r="D111" t="inlineStr"/>
-      <c r="E111" t="inlineStr"/>
-      <c r="F111" t="inlineStr"/>
-      <c r="G111" t="inlineStr"/>
-      <c r="H111" t="inlineStr"/>
-      <c r="I111" t="inlineStr"/>
-      <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr">
         <is>
-          <t>2. Fill the "Account Number" filter with "AC000107".</t>
+          <t>1. Verify the Master Bill To display shows the original address (City "WEST HOLLYWOOD").</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>"AC000107" is entered in the Account Number filter.</t>
+          <t>The Master Bill To display shows City "WEST HOLLYWOOD".</t>
         </is>
       </c>
       <c r="M111" t="inlineStr"/>
@@ -4475,12 +4478,12 @@
       <c r="J112" t="inlineStr"/>
       <c r="K112" t="inlineStr">
         <is>
-          <t>3. Click "Search". Confirm the results are filtered (allow up to 20 seconds for the server search).</t>
+          <t>2. Open the "Master" Address dialog.</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>The results table updates with the filtered match.</t>
+          <t>The Select Customer Address dialog opens.</t>
         </is>
       </c>
       <c r="M112" t="inlineStr"/>
@@ -4498,12 +4501,12 @@
       <c r="J113" t="inlineStr"/>
       <c r="K113" t="inlineStr">
         <is>
-          <t>4. Verify the results contain "Parker Palm Springs".</t>
+          <t>3. Select the alternate address row "4200 E Palm Canyon Dr" (PALM SPRINGS), then click "Select" and confirm the dialog closes.</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>The results table shows the entry "Parker Palm Springs".</t>
+          <t>The dialog closes after the address is selected.</t>
         </is>
       </c>
       <c r="M113" t="inlineStr"/>
@@ -4521,80 +4524,35 @@
       <c r="J114" t="inlineStr"/>
       <c r="K114" t="inlineStr">
         <is>
-          <t>5. Cancel the dialog</t>
+          <t>4. Verify the "Master" display fields update (City now shows "PALM SPRINGS").</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>The Account List dialog closes.</t>
+          <t>The Master display fields update to show City "PALM SPRINGS".</t>
         </is>
       </c>
       <c r="M114" t="inlineStr"/>
     </row>
     <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>TC-LOC-ACC-031</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>Address dialog search filter then clear restores full set</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>locations</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>account_address</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>User: automation user (location-edit permission)
-Location: test office 1604
-Application: Navigator
-Sample input 1: "Select Customer Address"
-Sample input 2: "Address"
-Sample input 3: "Beverly"</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>Automated</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J115" t="inlineStr">
-        <is>
-          <t>Office 1604 is open in Navigator. Account and Address tab is active</t>
-        </is>
-      </c>
+      <c r="A115" t="inlineStr"/>
+      <c r="B115" t="inlineStr"/>
+      <c r="C115" t="inlineStr"/>
+      <c r="D115" t="inlineStr"/>
+      <c r="E115" t="inlineStr"/>
+      <c r="F115" t="inlineStr"/>
+      <c r="G115" t="inlineStr"/>
+      <c r="H115" t="inlineStr"/>
+      <c r="I115" t="inlineStr"/>
+      <c r="J115" t="inlineStr"/>
       <c r="K115" t="inlineStr">
         <is>
-          <t>1. Open the "Select Customer Address" dialog from the Venue "Address" button. Confirm 7 rows are visible (Total Addresses: 7).</t>
+          <t>5. Verify the "Venue/Branch" display is UNCHANGED (still "WEST HOLLYWOOD") - the Master selection is isolated from Venue.</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>Seven address rows are displayed with "Total Addresses: 7" shown in the footer.</t>
+          <t>The Venue/Branch display remains unchanged, still showing "WEST HOLLYWOOD".</t>
         </is>
       </c>
       <c r="M115" t="inlineStr"/>
@@ -4612,12 +4570,12 @@
       <c r="J116" t="inlineStr"/>
       <c r="K116" t="inlineStr">
         <is>
-          <t>2. Type "Beverly" in the search bar. Confirm the rows are reduced by the filter.</t>
+          <t>6. Verify the left-panel "Save" is enabled (there are unsaved changes).</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>The row count reduces to matches containing "Beverly".</t>
+          <t>The left-panel Save button is enabled.</t>
         </is>
       </c>
       <c r="M116" t="inlineStr"/>
@@ -4635,35 +4593,81 @@
       <c r="J117" t="inlineStr"/>
       <c r="K117" t="inlineStr">
         <is>
-          <t>3. Clear the search bar.</t>
+          <t>7. Reload the page WITHOUT saving and verify the Master display reverts to the original address (no persist without save)</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>The search bar becomes empty.</t>
+          <t>Selecting an address from the "Master" picker dialog updates ONLY the Master display fields (Venue is untouched) and enables Save; reloading without saving discards the change</t>
         </is>
       </c>
       <c r="M117" t="inlineStr"/>
     </row>
     <row r="118">
-      <c r="A118" t="inlineStr"/>
-      <c r="B118" t="inlineStr"/>
-      <c r="C118" t="inlineStr"/>
-      <c r="D118" t="inlineStr"/>
-      <c r="E118" t="inlineStr"/>
-      <c r="F118" t="inlineStr"/>
-      <c r="G118" t="inlineStr"/>
-      <c r="H118" t="inlineStr"/>
-      <c r="I118" t="inlineStr"/>
-      <c r="J118" t="inlineStr"/>
+      <c r="A118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-LOC-ACC-031</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Master Bill To selection persists through save+reload (restore anchored original)</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>locations</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>account_address</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>User: automation user (location-edit permission)
+Location: test office 1604
+Application: Navigator
+Sample input 1: "4200 E Palm Canyon Dr"
+Sample input 2: "Save Changes"
+Sample input 3: "PALM SPRINGS"
+Sample input 4: "8899 Beverly Blvd Ste 412"</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>Office 1604 is open in Navigator. Account and Address tab is active</t>
+        </is>
+      </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>4. Verify the rows restore to the full 7-row set.</t>
+          <t>1. Confirm the Master display is anchored at the original address (8899 Beverly Blvd Ste 412 / WEST HOLLYWOOD) before any change.</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>The full set of 7 address rows is restored.</t>
+          <t>The Master display shows the original address "8899 Beverly Blvd Ste 412" / "WEST HOLLYWOOD".</t>
         </is>
       </c>
       <c r="M118" t="inlineStr"/>
@@ -4681,83 +4685,35 @@
       <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr">
         <is>
-          <t>5. Cancel the dialog</t>
+          <t>2. Open the Master Address dialog, select "4200 E Palm Canyon Dr", then click "Save" and confirm "Save Changes" (Ok).</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>The Account List dialog closes.</t>
+          <t>The changes are saved and the Save button becomes disabled.</t>
         </is>
       </c>
       <c r="M119" t="inlineStr"/>
     </row>
     <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>TC-LOC-ACC-032</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>Master Bill To selection updates Master display + leaves Venue unchanged + enables Save</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>locations</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>account_address</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>User: automation user (location-edit permission)
-Location: test office 1604
-Application: Navigator
-Sample input 1: "WEST HOLLYWOOD"
-Sample input 2: "Master"
-Sample input 3: "4200 E Palm Canyon Dr"
-Sample input 4: "Select"
-Sample input 5: "PALM SPRINGS"
-Sample input 6: "Venue/Branch"</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>Automated</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J120" t="inlineStr">
-        <is>
-          <t>Office 1604 is open in Navigator. Account and Address tab is active</t>
-        </is>
-      </c>
+      <c r="A120" t="inlineStr"/>
+      <c r="B120" t="inlineStr"/>
+      <c r="C120" t="inlineStr"/>
+      <c r="D120" t="inlineStr"/>
+      <c r="E120" t="inlineStr"/>
+      <c r="F120" t="inlineStr"/>
+      <c r="G120" t="inlineStr"/>
+      <c r="H120" t="inlineStr"/>
+      <c r="I120" t="inlineStr"/>
+      <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr">
         <is>
-          <t>1. Verify the Master Bill To display shows the original address (City "WEST HOLLYWOOD").</t>
+          <t>3. Reload the page and verify the Master Bill To now shows "PALM SPRINGS" with the address "4200 E Palm Canyon Dr".</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>The Master Bill To display shows City "WEST HOLLYWOOD".</t>
+          <t>The Master Bill To display shows "PALM SPRINGS" with address "4200 E Palm Canyon Dr".</t>
         </is>
       </c>
       <c r="M120" t="inlineStr"/>
@@ -4775,300 +4731,47 @@
       <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr">
         <is>
-          <t>2. Open the "Master" Address dialog.</t>
+          <t>4. Restore: open the Master Address dialog again, select "8899 Beverly Blvd Ste 412", click "Save" and confirm (Ok), reload the page, and verify all five Master values (address, city, state, zip, country) are back to the anchored original</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>The Select Customer Address dialog opens.</t>
+          <t>A Master Bill To selection persists through save and reload - unlike the Venue address selection, which does not persist. Same dialog, opposite persistence per picker dialog. Office 1604 is restored to its anchored original (8899 Beverly Blvd Ste 412), so nothing leaks</t>
         </is>
       </c>
       <c r="M121" t="inlineStr"/>
     </row>
-    <row r="122">
-      <c r="A122" t="inlineStr"/>
-      <c r="B122" t="inlineStr"/>
-      <c r="C122" t="inlineStr"/>
-      <c r="D122" t="inlineStr"/>
-      <c r="E122" t="inlineStr"/>
-      <c r="F122" t="inlineStr"/>
-      <c r="G122" t="inlineStr"/>
-      <c r="H122" t="inlineStr"/>
-      <c r="I122" t="inlineStr"/>
-      <c r="J122" t="inlineStr"/>
-      <c r="K122" t="inlineStr">
-        <is>
-          <t>3. Select the alternate address row "4200 E Palm Canyon Dr" (PALM SPRINGS), then click "Select" and confirm the dialog closes.</t>
-        </is>
-      </c>
-      <c r="L122" t="inlineStr">
-        <is>
-          <t>The dialog closes after the address is selected.</t>
-        </is>
-      </c>
-      <c r="M122" t="inlineStr"/>
-    </row>
+    <row r="122"/>
     <row r="123">
-      <c r="A123" t="inlineStr"/>
-      <c r="B123" t="inlineStr"/>
-      <c r="C123" t="inlineStr"/>
-      <c r="D123" t="inlineStr"/>
-      <c r="E123" t="inlineStr"/>
-      <c r="F123" t="inlineStr"/>
-      <c r="G123" t="inlineStr"/>
-      <c r="H123" t="inlineStr"/>
-      <c r="I123" t="inlineStr"/>
-      <c r="J123" t="inlineStr"/>
-      <c r="K123" t="inlineStr">
-        <is>
-          <t>4. Verify the "Master" display fields update (City now shows "PALM SPRINGS").</t>
-        </is>
-      </c>
-      <c r="L123" t="inlineStr">
-        <is>
-          <t>The Master display fields update to show City "PALM SPRINGS".</t>
-        </is>
-      </c>
-      <c r="M123" t="inlineStr"/>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr"/>
-      <c r="B124" t="inlineStr"/>
-      <c r="C124" t="inlineStr"/>
-      <c r="D124" t="inlineStr"/>
-      <c r="E124" t="inlineStr"/>
-      <c r="F124" t="inlineStr"/>
-      <c r="G124" t="inlineStr"/>
-      <c r="H124" t="inlineStr"/>
-      <c r="I124" t="inlineStr"/>
-      <c r="J124" t="inlineStr"/>
-      <c r="K124" t="inlineStr">
-        <is>
-          <t>5. Verify the "Venue/Branch" display is UNCHANGED (still "WEST HOLLYWOOD") - the Master selection is isolated from Venue.</t>
-        </is>
-      </c>
-      <c r="L124" t="inlineStr">
-        <is>
-          <t>The Venue/Branch display remains unchanged, still showing "WEST HOLLYWOOD".</t>
-        </is>
-      </c>
-      <c r="M124" t="inlineStr"/>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr"/>
-      <c r="B125" t="inlineStr"/>
-      <c r="C125" t="inlineStr"/>
-      <c r="D125" t="inlineStr"/>
-      <c r="E125" t="inlineStr"/>
-      <c r="F125" t="inlineStr"/>
-      <c r="G125" t="inlineStr"/>
-      <c r="H125" t="inlineStr"/>
-      <c r="I125" t="inlineStr"/>
-      <c r="J125" t="inlineStr"/>
-      <c r="K125" t="inlineStr">
-        <is>
-          <t>6. Verify the left-panel "Save" is enabled (there are unsaved changes).</t>
-        </is>
-      </c>
-      <c r="L125" t="inlineStr">
-        <is>
-          <t>The left-panel Save button is enabled.</t>
-        </is>
-      </c>
-      <c r="M125" t="inlineStr"/>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr"/>
-      <c r="B126" t="inlineStr"/>
-      <c r="C126" t="inlineStr"/>
-      <c r="D126" t="inlineStr"/>
-      <c r="E126" t="inlineStr"/>
-      <c r="F126" t="inlineStr"/>
-      <c r="G126" t="inlineStr"/>
-      <c r="H126" t="inlineStr"/>
-      <c r="I126" t="inlineStr"/>
-      <c r="J126" t="inlineStr"/>
-      <c r="K126" t="inlineStr">
-        <is>
-          <t>7. Reload the page WITHOUT saving and verify the Master display reverts to the original address (no persist without save)</t>
-        </is>
-      </c>
-      <c r="L126" t="inlineStr">
-        <is>
-          <t>Selecting an address from the "Master" picker dialog updates ONLY the Master display fields (Venue is untouched) and enables Save; reloading without saving discards the change</t>
-        </is>
-      </c>
-      <c r="M126" t="inlineStr"/>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>TC-LOC-ACC-033</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>Master Bill To selection persists through save+reload (restore anchored original)</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>locations</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>account_address</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>User: automation user (location-edit permission)
-Location: test office 1604
-Application: Navigator
-Sample input 1: "4200 E Palm Canyon Dr"
-Sample input 2: "Save Changes"
-Sample input 3: "PALM SPRINGS"
-Sample input 4: "8899 Beverly Blvd Ste 412"</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>Automated</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J127" t="inlineStr">
-        <is>
-          <t>Office 1604 is open in Navigator. Account and Address tab is active</t>
-        </is>
-      </c>
-      <c r="K127" t="inlineStr">
-        <is>
-          <t>1. Confirm the Master display is anchored at the original address (8899 Beverly Blvd Ste 412 / WEST HOLLYWOOD) before any change.</t>
-        </is>
-      </c>
-      <c r="L127" t="inlineStr">
-        <is>
-          <t>The Master display shows the original address "8899 Beverly Blvd Ste 412" / "WEST HOLLYWOOD".</t>
-        </is>
-      </c>
-      <c r="M127" t="inlineStr"/>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr"/>
-      <c r="B128" t="inlineStr"/>
-      <c r="C128" t="inlineStr"/>
-      <c r="D128" t="inlineStr"/>
-      <c r="E128" t="inlineStr"/>
-      <c r="F128" t="inlineStr"/>
-      <c r="G128" t="inlineStr"/>
-      <c r="H128" t="inlineStr"/>
-      <c r="I128" t="inlineStr"/>
-      <c r="J128" t="inlineStr"/>
-      <c r="K128" t="inlineStr">
-        <is>
-          <t>2. Open the Master Address dialog, select "4200 E Palm Canyon Dr", then click "Save" and confirm "Save Changes" (Ok).</t>
-        </is>
-      </c>
-      <c r="L128" t="inlineStr">
-        <is>
-          <t>The changes are saved and the Save button becomes disabled.</t>
-        </is>
-      </c>
-      <c r="M128" t="inlineStr"/>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr"/>
-      <c r="B129" t="inlineStr"/>
-      <c r="C129" t="inlineStr"/>
-      <c r="D129" t="inlineStr"/>
-      <c r="E129" t="inlineStr"/>
-      <c r="F129" t="inlineStr"/>
-      <c r="G129" t="inlineStr"/>
-      <c r="H129" t="inlineStr"/>
-      <c r="I129" t="inlineStr"/>
-      <c r="J129" t="inlineStr"/>
-      <c r="K129" t="inlineStr">
-        <is>
-          <t>3. Reload the page and verify the Master Bill To now shows "PALM SPRINGS" with the address "4200 E Palm Canyon Dr".</t>
-        </is>
-      </c>
-      <c r="L129" t="inlineStr">
-        <is>
-          <t>The Master Bill To display shows "PALM SPRINGS" with address "4200 E Palm Canyon Dr".</t>
-        </is>
-      </c>
-      <c r="M129" t="inlineStr"/>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr"/>
-      <c r="B130" t="inlineStr"/>
-      <c r="C130" t="inlineStr"/>
-      <c r="D130" t="inlineStr"/>
-      <c r="E130" t="inlineStr"/>
-      <c r="F130" t="inlineStr"/>
-      <c r="G130" t="inlineStr"/>
-      <c r="H130" t="inlineStr"/>
-      <c r="I130" t="inlineStr"/>
-      <c r="J130" t="inlineStr"/>
-      <c r="K130" t="inlineStr">
-        <is>
-          <t>4. Restore: open the Master Address dialog again, select "8899 Beverly Blvd Ste 412", click "Save" and confirm (Ok), reload the page, and verify all five Master values (address, city, state, zip, country) are back to the anchored original</t>
-        </is>
-      </c>
-      <c r="L130" t="inlineStr">
-        <is>
-          <t>A Master Bill To selection persists through save and reload - unlike the Venue address selection, which does not persist. Same dialog, opposite persistence per picker dialog. Office 1604 is restored to its anchored original (8899 Beverly Blvd Ste 412), so nothing leaks</t>
-        </is>
-      </c>
-      <c r="M130" t="inlineStr"/>
-    </row>
-    <row r="131"/>
-    <row r="132">
-      <c r="A132" s="2" t="inlineStr">
+      <c r="A123" s="2" t="inlineStr">
         <is>
           <t>SUMMARY</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
+      <c r="B123" s="2" t="inlineStr">
         <is>
           <t>Location — Account &amp; Address</t>
         </is>
       </c>
-      <c r="C132" s="2" t="inlineStr"/>
-      <c r="D132" s="2" t="inlineStr"/>
-      <c r="E132" s="2" t="inlineStr"/>
-      <c r="F132" s="2" t="inlineStr"/>
-      <c r="G132" s="2" t="inlineStr"/>
-      <c r="H132" s="2" t="inlineStr">
-        <is>
-          <t>Automated: 31 / Pending: 2</t>
-        </is>
-      </c>
-      <c r="I132" s="2" t="inlineStr">
+      <c r="C123" s="2" t="inlineStr"/>
+      <c r="D123" s="2" t="inlineStr"/>
+      <c r="E123" s="2" t="inlineStr"/>
+      <c r="F123" s="2" t="inlineStr"/>
+      <c r="G123" s="2" t="inlineStr"/>
+      <c r="H123" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Automated: 31 / Pending: 0</t>
+        </is>
+      </c>
+      <c r="I123" s="2" t="inlineStr">
         <is>
           <t>Pass:22 Fail:0 Skipped:0 Blocked:9</t>
         </is>
       </c>
-      <c r="J132" s="2" t="inlineStr"/>
-      <c r="K132" s="2" t="inlineStr"/>
-      <c r="L132" s="2" t="inlineStr"/>
-      <c r="M132" s="2" t="inlineStr">
+      <c r="J123" s="2" t="inlineStr"/>
+      <c r="K123" s="2" t="inlineStr"/>
+      <c r="L123" s="2" t="inlineStr"/>
+      <c r="M123" s="2" t="inlineStr">
         <is>
           <t>Last Updated: 2026-08-12</t>
         </is>
